--- a/crates/runtime/tests/fixtures/documents/roster.xlsx
+++ b/crates/runtime/tests/fixtures/documents/roster.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,7 +428,7 @@
           <t>Status        Units</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
@@ -445,7 +445,7 @@
           <t>Enrolled      1.00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -463,7 +463,7 @@
           <t>Enrolled      3.00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
